--- a/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/BU 03/HRM/pre LAM_HRM-2031-0160/Panel-28/back/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU03_Back_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/BU 03/HRM/pre LAM_HRM-2031-0160/Panel-28/back/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU03_Back_Summary.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H30"/>
+  <dimension ref="A1:H20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -460,22 +460,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>17.03611</v>
+        <v>16.63066</v>
       </c>
       <c r="D2" t="n">
-        <v>16.76502</v>
+        <v>16.33068</v>
       </c>
       <c r="E2" t="n">
-        <v>16.84255</v>
+        <v>16.60194</v>
       </c>
       <c r="F2" t="n">
-        <v>43.17916</v>
+        <v>42.84911</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05129</v>
+        <v>0.05054</v>
       </c>
       <c r="H2" t="n">
-        <v>1.8241</v>
+        <v>1.81578</v>
       </c>
     </row>
     <row r="3">
@@ -485,22 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>16.9242</v>
+        <v>16.95251</v>
       </c>
       <c r="D3" t="n">
-        <v>16.92249</v>
+        <v>16.45756</v>
       </c>
       <c r="E3" t="n">
-        <v>17.30914</v>
+        <v>16.7441</v>
       </c>
       <c r="F3" t="n">
-        <v>42.03901</v>
+        <v>42.32643</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05001</v>
+        <v>0.0509</v>
       </c>
       <c r="H3" t="n">
-        <v>1.84934</v>
+        <v>1.84254</v>
       </c>
     </row>
     <row r="4">
@@ -510,22 +510,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>16.8159</v>
+        <v>16.96614</v>
       </c>
       <c r="D4" t="n">
-        <v>16.77779</v>
+        <v>16.52488</v>
       </c>
       <c r="E4" t="n">
-        <v>16.72695</v>
+        <v>16.79746</v>
       </c>
       <c r="F4" t="n">
-        <v>43.46018</v>
+        <v>43.86522</v>
       </c>
       <c r="G4" t="n">
-        <v>0.051</v>
+        <v>0.05141</v>
       </c>
       <c r="H4" t="n">
-        <v>1.83594</v>
+        <v>1.84935</v>
       </c>
     </row>
     <row r="5">
@@ -535,22 +535,22 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>17.19282</v>
+        <v>16.95341</v>
       </c>
       <c r="D5" t="n">
-        <v>16.8394</v>
+        <v>16.75633</v>
       </c>
       <c r="E5" t="n">
-        <v>16.89026</v>
+        <v>16.803</v>
       </c>
       <c r="F5" t="n">
-        <v>42.34273</v>
+        <v>42.37663</v>
       </c>
       <c r="G5" t="n">
-        <v>0.05003</v>
+        <v>0.05105</v>
       </c>
       <c r="H5" t="n">
-        <v>1.78691</v>
+        <v>1.83216</v>
       </c>
     </row>
     <row r="6">
@@ -559,23 +559,10 @@
           <t>Unit 5</t>
         </is>
       </c>
-      <c r="C6" t="n">
-        <v>17.10322</v>
-      </c>
-      <c r="D6" t="n">
-        <v>16.75876</v>
-      </c>
-      <c r="E6" t="n">
-        <v>17.12424</v>
-      </c>
-      <c r="F6" t="n">
-        <v>42.00491</v>
-      </c>
-      <c r="G6" t="n">
-        <v>0.0507</v>
-      </c>
-      <c r="H6" t="n">
-        <v>1.78153</v>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>scratched - not measurable</t>
+        </is>
       </c>
     </row>
     <row r="7">
@@ -585,22 +572,22 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>16.9356</v>
+        <v>16.93961</v>
       </c>
       <c r="D7" t="n">
-        <v>16.57566</v>
+        <v>16.70099</v>
       </c>
       <c r="E7" t="n">
-        <v>16.64468</v>
+        <v>16.72826</v>
       </c>
       <c r="F7" t="n">
-        <v>42.3646</v>
+        <v>42.69686</v>
       </c>
       <c r="G7" t="n">
-        <v>0.05168</v>
+        <v>0.04961</v>
       </c>
       <c r="H7" t="n">
-        <v>1.79537</v>
+        <v>1.829</v>
       </c>
     </row>
     <row r="8">
@@ -610,22 +597,22 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>16.72902</v>
+        <v>17.03117</v>
       </c>
       <c r="D8" t="n">
-        <v>16.69649</v>
+        <v>16.63141</v>
       </c>
       <c r="E8" t="n">
-        <v>16.88996</v>
+        <v>16.89389</v>
       </c>
       <c r="F8" t="n">
-        <v>42.49959</v>
+        <v>41.90655</v>
       </c>
       <c r="G8" t="n">
-        <v>0.05173</v>
+        <v>0.05089</v>
       </c>
       <c r="H8" t="n">
-        <v>1.80271</v>
+        <v>1.79667</v>
       </c>
     </row>
     <row r="9">
@@ -635,22 +622,22 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>17.33721</v>
+        <v>17.16287</v>
       </c>
       <c r="D9" t="n">
-        <v>16.86348</v>
+        <v>16.74283</v>
       </c>
       <c r="E9" t="n">
-        <v>16.95233</v>
+        <v>16.75735</v>
       </c>
       <c r="F9" t="n">
-        <v>42.51362</v>
+        <v>42.68242</v>
       </c>
       <c r="G9" t="n">
-        <v>0.05169</v>
+        <v>0.05179</v>
       </c>
       <c r="H9" t="n">
-        <v>1.82796</v>
+        <v>1.81586</v>
       </c>
     </row>
     <row r="10">
@@ -660,22 +647,22 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>16.74886</v>
+        <v>17.46201</v>
       </c>
       <c r="D10" t="n">
-        <v>16.74576</v>
+        <v>16.89535</v>
       </c>
       <c r="E10" t="n">
-        <v>16.79476</v>
+        <v>16.9916</v>
       </c>
       <c r="F10" t="n">
-        <v>43.11991</v>
+        <v>42.41444</v>
       </c>
       <c r="G10" t="n">
-        <v>0.05095</v>
+        <v>0.05168</v>
       </c>
       <c r="H10" t="n">
-        <v>1.84024</v>
+        <v>1.86451</v>
       </c>
     </row>
     <row r="11">
@@ -696,17 +683,12 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Radius</t>
+          <t>Width</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dimple</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Bump</t>
+          <t>Space</t>
         </is>
       </c>
     </row>
@@ -718,26 +700,23 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Pad 1</t>
+          <t>Trace 1</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>16.84913</v>
+        <v>16.71631</v>
       </c>
       <c r="D12" t="n">
-        <v>16.82793</v>
+        <v>15.94017</v>
       </c>
       <c r="E12" t="n">
-        <v>16.7739</v>
+        <v>16.44895</v>
       </c>
       <c r="F12" t="n">
-        <v>42.85926</v>
+        <v>21.96525</v>
       </c>
       <c r="G12" t="n">
-        <v>0.051</v>
-      </c>
-      <c r="H12" t="n">
-        <v>1.82193</v>
+        <v>33.90529</v>
       </c>
     </row>
     <row r="13">
@@ -747,22 +726,19 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>16.87543</v>
+        <v>16.92188</v>
       </c>
       <c r="D13" t="n">
-        <v>16.27211</v>
+        <v>16.17702</v>
       </c>
       <c r="E13" t="n">
-        <v>16.7658</v>
+        <v>16.3312</v>
       </c>
       <c r="F13" t="n">
-        <v>42.74359</v>
+        <v>22.10927</v>
       </c>
       <c r="G13" t="n">
-        <v>0.05071</v>
-      </c>
-      <c r="H13" t="n">
-        <v>1.85795</v>
+        <v>34.28074</v>
       </c>
     </row>
     <row r="14">
@@ -771,23 +747,25 @@
           <t>Unit 9</t>
         </is>
       </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>re-measured</t>
+        </is>
+      </c>
       <c r="C14" t="n">
-        <v>16.56306</v>
+        <v>16.92165</v>
       </c>
       <c r="D14" t="n">
-        <v>16.69244</v>
+        <v>16.01406</v>
       </c>
       <c r="E14" t="n">
-        <v>16.46944</v>
+        <v>16.55776</v>
       </c>
       <c r="F14" t="n">
-        <v>43.42414</v>
+        <v>21.66408</v>
       </c>
       <c r="G14" t="n">
-        <v>0.05109</v>
-      </c>
-      <c r="H14" t="n">
-        <v>1.82649</v>
+        <v>34.93763</v>
       </c>
     </row>
     <row r="15">
@@ -797,22 +775,19 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>16.86972</v>
+        <v>16.68942</v>
       </c>
       <c r="D15" t="n">
-        <v>16.98551</v>
+        <v>16.02398</v>
       </c>
       <c r="E15" t="n">
-        <v>16.64534</v>
+        <v>16.3033</v>
       </c>
       <c r="F15" t="n">
-        <v>42.9908</v>
+        <v>21.53606</v>
       </c>
       <c r="G15" t="n">
-        <v>0.05151</v>
-      </c>
-      <c r="H15" t="n">
-        <v>1.90495</v>
+        <v>34.3467</v>
       </c>
     </row>
     <row r="16">
@@ -822,22 +797,19 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>16.7638</v>
+        <v>16.85288</v>
       </c>
       <c r="D16" t="n">
-        <v>16.95097</v>
+        <v>15.8956</v>
       </c>
       <c r="E16" t="n">
-        <v>17.09135</v>
+        <v>16.40999</v>
       </c>
       <c r="F16" t="n">
-        <v>42.55061</v>
+        <v>21.55389</v>
       </c>
       <c r="G16" t="n">
-        <v>0.05044</v>
-      </c>
-      <c r="H16" t="n">
-        <v>1.82766</v>
+        <v>34.37209</v>
       </c>
     </row>
     <row r="17">
@@ -847,22 +819,19 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>16.95922</v>
+        <v>16.77071</v>
       </c>
       <c r="D17" t="n">
-        <v>16.45109</v>
+        <v>15.86772</v>
       </c>
       <c r="E17" t="n">
-        <v>16.92188</v>
+        <v>16.2861</v>
       </c>
       <c r="F17" t="n">
-        <v>43.00221</v>
+        <v>22.02404</v>
       </c>
       <c r="G17" t="n">
-        <v>0.0504</v>
-      </c>
-      <c r="H17" t="n">
-        <v>1.85101</v>
+        <v>34.61085</v>
       </c>
     </row>
     <row r="18">
@@ -872,22 +841,19 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>16.83611</v>
+        <v>16.93782</v>
       </c>
       <c r="D18" t="n">
-        <v>16.81909</v>
+        <v>16.33676</v>
       </c>
       <c r="E18" t="n">
-        <v>16.72355</v>
+        <v>16.56164</v>
       </c>
       <c r="F18" t="n">
-        <v>42.92752</v>
+        <v>21.83568</v>
       </c>
       <c r="G18" t="n">
-        <v>0.05038</v>
-      </c>
-      <c r="H18" t="n">
-        <v>1.86058</v>
+        <v>33.86443</v>
       </c>
     </row>
     <row r="19">
@@ -897,22 +863,19 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>16.79057</v>
+        <v>16.75317</v>
       </c>
       <c r="D19" t="n">
-        <v>16.63248</v>
+        <v>16.05137</v>
       </c>
       <c r="E19" t="n">
-        <v>16.60521</v>
+        <v>16.31597</v>
       </c>
       <c r="F19" t="n">
-        <v>42.07044</v>
+        <v>21.78377</v>
       </c>
       <c r="G19" t="n">
-        <v>0.05081</v>
-      </c>
-      <c r="H19" t="n">
-        <v>1.8385</v>
+        <v>33.51976</v>
       </c>
     </row>
     <row r="20">
@@ -922,156 +885,19 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>16.70044</v>
+        <v>16.99265</v>
       </c>
       <c r="D20" t="n">
-        <v>16.61258</v>
+        <v>16.20753</v>
       </c>
       <c r="E20" t="n">
-        <v>16.54136</v>
+        <v>16.60911</v>
       </c>
       <c r="F20" t="n">
-        <v>42.71088</v>
+        <v>21.79033</v>
       </c>
       <c r="G20" t="n">
-        <v>0.05082</v>
-      </c>
-      <c r="H20" t="n">
-        <v>1.80772</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Dimple</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Bump</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Unit 7</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>via 1</t>
-        </is>
-      </c>
-      <c r="C22" t="n">
-        <v>0.60319</v>
-      </c>
-      <c r="D22" t="n">
-        <v>1.12681</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Unit 8</t>
-        </is>
-      </c>
-      <c r="C23" t="n">
-        <v>0.61439</v>
-      </c>
-      <c r="D23" t="n">
-        <v>1.12919</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Unit 9</t>
-        </is>
-      </c>
-      <c r="C24" t="n">
-        <v>0.62038</v>
-      </c>
-      <c r="D24" t="n">
-        <v>1.12456</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Unit 4</t>
-        </is>
-      </c>
-      <c r="C25" t="n">
-        <v>0.60937</v>
-      </c>
-      <c r="D25" t="n">
-        <v>1.1021</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Unit 5</t>
-        </is>
-      </c>
-      <c r="C26" t="n">
-        <v>0.60921</v>
-      </c>
-      <c r="D26" t="n">
-        <v>1.13592</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Unit 6</t>
-        </is>
-      </c>
-      <c r="C27" t="n">
-        <v>0.5945</v>
-      </c>
-      <c r="D27" t="n">
-        <v>1.11452</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Unit 1</t>
-        </is>
-      </c>
-      <c r="C28" t="n">
-        <v>0.5950299999999999</v>
-      </c>
-      <c r="D28" t="n">
-        <v>1.13284</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Unit 2</t>
-        </is>
-      </c>
-      <c r="C29" t="n">
-        <v>0.61548</v>
-      </c>
-      <c r="D29" t="n">
-        <v>1.12778</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Unit 3</t>
-        </is>
-      </c>
-      <c r="C30" t="n">
-        <v>0.6081</v>
-      </c>
-      <c r="D30" t="n">
-        <v>1.11233</v>
+        <v>34.17901</v>
       </c>
     </row>
   </sheetData>
